--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#20</t>
+          <t>#21</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#21</t>
+          <t>#22</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#22</t>
+          <t>#23</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#23</t>
+          <t>#24</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#24</t>
+          <t>#25</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#25</t>
+          <t>#26</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#26</t>
+          <t>#27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#27</t>
+          <t>#28</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/web/Excel/Summary_Report.xlsx
+++ b/reports/latest/web/Excel/Summary_Report.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#28</t>
+          <t>#29</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
